--- a/data/historicalweeklydata.xlsx
+++ b/data/historicalweeklydata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046DE1D7-CE4C-4C00-8B3E-5B5C1A23DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2BA69B-0B15-4250-B19E-BD594C07A16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="689" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26055" yWindow="1770" windowWidth="22575" windowHeight="13290" tabRatio="689" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Full History" sheetId="3" r:id="rId1"/>
@@ -53,14 +53,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00_)"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
+    <numFmt numFmtId="166" formatCode="General_)"/>
   </numFmts>
-  <fonts count="192">
+  <fonts count="194">
     <font>
       <sz val="12"/>
       <name val="Helv"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -911,6 +919,10 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Helv"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Helv"/>
     </font>
   </fonts>
@@ -1220,50 +1232,70 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="223">
+  <cellStyleXfs count="243">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1445,352 +1477,357 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="173">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="127" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="128" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="129" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="127" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="130" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="128" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="131" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="129" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="132" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="130" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="131" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="134" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="132" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="135" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="136" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="134" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="137" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="135" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="138" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="136" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="139" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="137" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="140" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="138" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="141" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="139" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="142" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="140" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="143" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="141" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="144" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="142" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="145" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="143" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="146" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="144" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="147" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="145" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="148" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="146" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="149" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="147" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="150" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="148" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="151" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="149" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="152" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="150" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="153" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="151" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="154" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="152" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="155" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="153" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="156" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="154" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="157" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="155" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="158" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="156" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="159" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="157" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="160" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="158" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="161" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="159" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="162" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="160" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="163" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="161" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="164" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="162" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="165" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="163" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="166" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="164" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="167" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="165" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="168" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="166" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="169" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="167" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="170" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="168" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="171" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="169" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="172" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="170" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="173" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="171" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="174" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="172" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="175" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="173" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="176" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="174" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="177" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="175" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="178" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="176" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="179" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="177" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="180" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="178" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="181" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="179" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="182" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="180" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="183" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="181" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="184" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="182" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="185" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="183" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="186" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="184" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="187" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="185" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="188" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="186" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="189" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="187" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="190" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="188" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="191" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="189" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="192" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="190" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="191" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="223">
+  <cellStyles count="243">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent1 10" xfId="203" xr:uid="{5C306DFA-D090-4999-947C-579E25C93A97}"/>
+    <cellStyle name="20% - Accent1 11" xfId="223" xr:uid="{ECBEA576-0FEF-4E97-B3DC-DA1CC35197E2}"/>
     <cellStyle name="20% - Accent1 2" xfId="43" xr:uid="{546FFBA8-3F00-4C29-9A97-E66E12731BA1}"/>
     <cellStyle name="20% - Accent1 3" xfId="63" xr:uid="{CA635C99-7D92-4623-810A-59FB7B0834E1}"/>
     <cellStyle name="20% - Accent1 4" xfId="83" xr:uid="{97EE4CD2-A075-4056-9755-87D85DD24135}"/>
@@ -1801,6 +1838,7 @@
     <cellStyle name="20% - Accent1 9" xfId="183" xr:uid="{21D126D3-1F6B-417B-890D-D4F4F2D013A3}"/>
     <cellStyle name="20% - Accent2" xfId="2" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent2 10" xfId="204" xr:uid="{5334DFBC-89EA-4EA0-9A22-D49214BF3377}"/>
+    <cellStyle name="20% - Accent2 11" xfId="224" xr:uid="{ED59378C-4A94-46D5-9ECD-08935F8219DF}"/>
     <cellStyle name="20% - Accent2 2" xfId="44" xr:uid="{45E5E8CF-1F82-4176-9AF9-F337A958863E}"/>
     <cellStyle name="20% - Accent2 3" xfId="64" xr:uid="{3792B714-AC32-4FF2-90F3-0F3ED3A81936}"/>
     <cellStyle name="20% - Accent2 4" xfId="84" xr:uid="{5D29E6EE-8FB9-481F-B820-8F70A0C61131}"/>
@@ -1811,6 +1849,7 @@
     <cellStyle name="20% - Accent2 9" xfId="184" xr:uid="{DBD0700D-E901-4958-B820-F927B896C519}"/>
     <cellStyle name="20% - Accent3" xfId="3" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - Accent3 10" xfId="205" xr:uid="{4B24DB49-0057-49FC-952E-F1368B60EC3C}"/>
+    <cellStyle name="20% - Accent3 11" xfId="225" xr:uid="{1499EB0D-760F-4CA8-B588-25830C9E1CCA}"/>
     <cellStyle name="20% - Accent3 2" xfId="45" xr:uid="{3E145216-3F80-4F8B-A663-45502BD76B67}"/>
     <cellStyle name="20% - Accent3 3" xfId="65" xr:uid="{44CF7697-8A26-46CA-8925-B516CCC0DFE8}"/>
     <cellStyle name="20% - Accent3 4" xfId="85" xr:uid="{1FCFA46F-6028-4615-93AE-1CE11176FA61}"/>
@@ -1821,6 +1860,7 @@
     <cellStyle name="20% - Accent3 9" xfId="185" xr:uid="{219E1FD4-41C6-46A4-8C71-A62345FAC0FD}"/>
     <cellStyle name="20% - Accent4" xfId="4" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - Accent4 10" xfId="206" xr:uid="{6531B28D-192F-4598-9CCA-597C0DAD1C86}"/>
+    <cellStyle name="20% - Accent4 11" xfId="226" xr:uid="{DB101878-DE4B-45C9-BA05-5BB673AE02FF}"/>
     <cellStyle name="20% - Accent4 2" xfId="46" xr:uid="{EF6C8FF1-2EC3-4984-BC15-6EEAB167EED5}"/>
     <cellStyle name="20% - Accent4 3" xfId="66" xr:uid="{1AB26F85-FC00-44AE-933D-215B4C16B4CA}"/>
     <cellStyle name="20% - Accent4 4" xfId="86" xr:uid="{60DB99E3-4F45-472B-8725-F93AAB114DA8}"/>
@@ -1831,6 +1871,7 @@
     <cellStyle name="20% - Accent4 9" xfId="186" xr:uid="{700A58C4-0BB2-4E72-9DA3-0BF3F738F0B4}"/>
     <cellStyle name="20% - Accent5" xfId="5" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - Accent5 10" xfId="207" xr:uid="{2B31C532-B18C-44A5-B785-0F7058FD8B45}"/>
+    <cellStyle name="20% - Accent5 11" xfId="227" xr:uid="{D9D94A1E-D48A-4BAC-91A1-D2A41D80FC5B}"/>
     <cellStyle name="20% - Accent5 2" xfId="47" xr:uid="{6CDD9DB4-EE99-4B07-8489-F3010F791B2C}"/>
     <cellStyle name="20% - Accent5 3" xfId="67" xr:uid="{34C1E4B5-F81D-42C9-945B-DBBF558BC739}"/>
     <cellStyle name="20% - Accent5 4" xfId="87" xr:uid="{BDDB5AC5-22E2-4384-9ADB-73E71FDA3C78}"/>
@@ -1841,6 +1882,7 @@
     <cellStyle name="20% - Accent5 9" xfId="187" xr:uid="{B4C042B3-1C26-4651-9E1D-EA6CBF8F6211}"/>
     <cellStyle name="20% - Accent6" xfId="6" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - Accent6 10" xfId="208" xr:uid="{813A2C72-3F5B-4D02-A297-F6F4FC02478E}"/>
+    <cellStyle name="20% - Accent6 11" xfId="228" xr:uid="{7FEF44C0-E84E-45C3-8BF2-83F5DA7BDFC8}"/>
     <cellStyle name="20% - Accent6 2" xfId="48" xr:uid="{CA46C58F-C5BC-4557-93C1-569EEA1FA328}"/>
     <cellStyle name="20% - Accent6 3" xfId="68" xr:uid="{A39A1436-32E8-4C10-9413-0EB6C0CA1C7A}"/>
     <cellStyle name="20% - Accent6 4" xfId="88" xr:uid="{92926B60-05C0-4C01-8AF7-6E96DF44D782}"/>
@@ -1851,6 +1893,7 @@
     <cellStyle name="20% - Accent6 9" xfId="188" xr:uid="{F61E148C-0C99-4344-9571-3B916749EC98}"/>
     <cellStyle name="40% - Accent1" xfId="7" builtinId="31" customBuiltin="1"/>
     <cellStyle name="40% - Accent1 10" xfId="209" xr:uid="{64C11C50-084D-4ECE-A053-A639F0E4228B}"/>
+    <cellStyle name="40% - Accent1 11" xfId="229" xr:uid="{2CC57E4B-95CE-4455-A998-7B97A28D12D6}"/>
     <cellStyle name="40% - Accent1 2" xfId="49" xr:uid="{BBF4A775-AFAA-48A8-AE8D-71433E06E388}"/>
     <cellStyle name="40% - Accent1 3" xfId="69" xr:uid="{2032F66E-B11A-4013-9DF8-03F5AADB914B}"/>
     <cellStyle name="40% - Accent1 4" xfId="89" xr:uid="{975532C1-45D8-4B45-98C2-979A7CA798D3}"/>
@@ -1861,6 +1904,7 @@
     <cellStyle name="40% - Accent1 9" xfId="189" xr:uid="{644C616C-9C93-41FB-9A5A-1B189B38EB86}"/>
     <cellStyle name="40% - Accent2" xfId="8" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - Accent2 10" xfId="210" xr:uid="{B7488FFC-EE68-4D94-AFB3-89DABE6158B0}"/>
+    <cellStyle name="40% - Accent2 11" xfId="230" xr:uid="{9929FFE8-3E67-4E59-84D5-EF334100B5A8}"/>
     <cellStyle name="40% - Accent2 2" xfId="50" xr:uid="{4A556E51-B599-40A1-8ECB-E7EE4E592ABD}"/>
     <cellStyle name="40% - Accent2 3" xfId="70" xr:uid="{4D3EE49A-E2A9-4CA4-874E-8C1FA9229518}"/>
     <cellStyle name="40% - Accent2 4" xfId="90" xr:uid="{547FBA07-8281-470B-8A20-EA76BAA8C8C5}"/>
@@ -1871,6 +1915,7 @@
     <cellStyle name="40% - Accent2 9" xfId="190" xr:uid="{36AFAE70-133C-4048-A4E0-A3DF1C854683}"/>
     <cellStyle name="40% - Accent3" xfId="9" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - Accent3 10" xfId="211" xr:uid="{5027FBDF-625E-4E5F-ADD3-92EFA8DE324F}"/>
+    <cellStyle name="40% - Accent3 11" xfId="231" xr:uid="{7A1D00E1-EBEB-4A67-9051-E580A09023CA}"/>
     <cellStyle name="40% - Accent3 2" xfId="51" xr:uid="{122A08BD-71FC-4089-B75E-E1CC8FC3CEA3}"/>
     <cellStyle name="40% - Accent3 3" xfId="71" xr:uid="{1882A769-DD86-4D03-816F-2F13917B9B60}"/>
     <cellStyle name="40% - Accent3 4" xfId="91" xr:uid="{51A66BB2-E3E3-4571-8780-3D565D9E2AC4}"/>
@@ -1881,6 +1926,7 @@
     <cellStyle name="40% - Accent3 9" xfId="191" xr:uid="{5645209F-470B-41D8-8192-9DEDED8790BA}"/>
     <cellStyle name="40% - Accent4" xfId="10" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - Accent4 10" xfId="212" xr:uid="{522BCEBE-67FC-4B7C-AC27-A763FA1E148A}"/>
+    <cellStyle name="40% - Accent4 11" xfId="232" xr:uid="{7DF1C062-ABB0-4520-9C93-AD88EF58475D}"/>
     <cellStyle name="40% - Accent4 2" xfId="52" xr:uid="{876E4C52-3977-44CE-9E48-53E7B777E06B}"/>
     <cellStyle name="40% - Accent4 3" xfId="72" xr:uid="{1C2D39E3-2D98-408B-B807-0D6D2357EDBF}"/>
     <cellStyle name="40% - Accent4 4" xfId="92" xr:uid="{FD8655A9-275D-48B2-B59E-30EF4F88A69B}"/>
@@ -1891,6 +1937,7 @@
     <cellStyle name="40% - Accent4 9" xfId="192" xr:uid="{7F08CA9E-1364-4D0F-AB78-6169066CAA4D}"/>
     <cellStyle name="40% - Accent5" xfId="11" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - Accent5 10" xfId="213" xr:uid="{BEBA0D18-E05A-432E-BCF8-B45873631E0A}"/>
+    <cellStyle name="40% - Accent5 11" xfId="233" xr:uid="{1251AEC2-FA97-49B8-8975-9592476876C7}"/>
     <cellStyle name="40% - Accent5 2" xfId="53" xr:uid="{005C4B2D-C53D-4080-A180-7EEF8BA47D8F}"/>
     <cellStyle name="40% - Accent5 3" xfId="73" xr:uid="{414E3342-EBD5-4638-ACEE-7F24E22A792D}"/>
     <cellStyle name="40% - Accent5 4" xfId="93" xr:uid="{548483D7-A968-4EC6-98D4-615CCBE4A77C}"/>
@@ -1901,6 +1948,7 @@
     <cellStyle name="40% - Accent5 9" xfId="193" xr:uid="{B3644043-3814-48DD-AD2F-AF07FB515C8F}"/>
     <cellStyle name="40% - Accent6" xfId="12" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - Accent6 10" xfId="214" xr:uid="{AA9E5DC4-F7FF-4982-A7C4-DB4232BF3006}"/>
+    <cellStyle name="40% - Accent6 11" xfId="234" xr:uid="{4CB82388-4063-4900-A606-B8F29E245586}"/>
     <cellStyle name="40% - Accent6 2" xfId="54" xr:uid="{4FDDF3A4-5626-4E53-9ADF-B2AAF0E0E534}"/>
     <cellStyle name="40% - Accent6 3" xfId="74" xr:uid="{F46B74EF-00D4-43AD-A556-C91E21F4B4E6}"/>
     <cellStyle name="40% - Accent6 4" xfId="94" xr:uid="{AF5DC496-7539-45CD-A24E-C69A3C819D35}"/>
@@ -1911,6 +1959,7 @@
     <cellStyle name="40% - Accent6 9" xfId="194" xr:uid="{C03D2A5C-DC22-4D55-93A5-E6D7F7CD9864}"/>
     <cellStyle name="60% - Accent1 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="60% - Accent1 2 10" xfId="215" xr:uid="{E21A31E0-7465-457E-9B98-C75D0C8273A6}"/>
+    <cellStyle name="60% - Accent1 2 11" xfId="235" xr:uid="{87D3CAF5-C90F-4524-A3CD-BA432A445797}"/>
     <cellStyle name="60% - Accent1 2 2" xfId="55" xr:uid="{0D2FA4FE-C2AA-49E9-9D9F-DB9375035D06}"/>
     <cellStyle name="60% - Accent1 2 3" xfId="75" xr:uid="{E6B67A6A-26E4-41BC-B34A-165C094B7C82}"/>
     <cellStyle name="60% - Accent1 2 4" xfId="95" xr:uid="{3F5CDF7D-0A34-4840-8CE8-E972FD1F186D}"/>
@@ -1921,6 +1970,7 @@
     <cellStyle name="60% - Accent1 2 9" xfId="195" xr:uid="{20938E60-6420-4F05-B86C-5A7387DCC9E3}"/>
     <cellStyle name="60% - Accent2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="60% - Accent2 2 10" xfId="216" xr:uid="{B22E4D66-9BB1-4775-9054-4B401784BF00}"/>
+    <cellStyle name="60% - Accent2 2 11" xfId="236" xr:uid="{23826167-6A28-44CC-BB18-699EE4160D77}"/>
     <cellStyle name="60% - Accent2 2 2" xfId="56" xr:uid="{2B644024-7F50-4EEC-BEB3-A70F78B73B5D}"/>
     <cellStyle name="60% - Accent2 2 3" xfId="76" xr:uid="{42ED8925-E8E3-4DB6-9A10-54B29F978BD3}"/>
     <cellStyle name="60% - Accent2 2 4" xfId="96" xr:uid="{E988E100-CD65-4383-B196-F48E77A2B551}"/>
@@ -1931,6 +1981,7 @@
     <cellStyle name="60% - Accent2 2 9" xfId="196" xr:uid="{B7B5E9F3-E381-48BA-B60B-9F3F71426C40}"/>
     <cellStyle name="60% - Accent3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="60% - Accent3 2 10" xfId="217" xr:uid="{5606D8A9-8047-4B6F-8100-31D0F1D8DB25}"/>
+    <cellStyle name="60% - Accent3 2 11" xfId="237" xr:uid="{2B4C587E-C0DA-48ED-B654-6CFE7B828F08}"/>
     <cellStyle name="60% - Accent3 2 2" xfId="57" xr:uid="{9A1DF08A-51FD-4E5C-9701-384F8396939D}"/>
     <cellStyle name="60% - Accent3 2 3" xfId="77" xr:uid="{190AA729-42E8-4F5F-9B95-BE3B56258C65}"/>
     <cellStyle name="60% - Accent3 2 4" xfId="97" xr:uid="{2069B6B1-9219-4834-AEF3-CF05347B1B0B}"/>
@@ -1941,6 +1992,7 @@
     <cellStyle name="60% - Accent3 2 9" xfId="197" xr:uid="{1386C7D3-85B4-4637-B846-C0A636FECFD4}"/>
     <cellStyle name="60% - Accent4 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="60% - Accent4 2 10" xfId="218" xr:uid="{F97C9131-DCCF-457F-8C15-CD3C2229141D}"/>
+    <cellStyle name="60% - Accent4 2 11" xfId="238" xr:uid="{67DF57E0-404B-491E-BC1C-41275312CF90}"/>
     <cellStyle name="60% - Accent4 2 2" xfId="58" xr:uid="{209C3B7C-98D3-4FD2-BB59-91D57E96990A}"/>
     <cellStyle name="60% - Accent4 2 3" xfId="78" xr:uid="{6F4D3AF3-DB69-4C19-8F7F-E6AD0FAD58C7}"/>
     <cellStyle name="60% - Accent4 2 4" xfId="98" xr:uid="{8C0BE291-2D6D-4D30-9620-5EA32591C56E}"/>
@@ -1951,6 +2003,7 @@
     <cellStyle name="60% - Accent4 2 9" xfId="198" xr:uid="{ABB3CFB5-F1D7-44AE-9146-090C34FC8FCE}"/>
     <cellStyle name="60% - Accent5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="60% - Accent5 2 10" xfId="219" xr:uid="{6011BADF-B4B9-4EA8-8EC3-1F801BE508C5}"/>
+    <cellStyle name="60% - Accent5 2 11" xfId="239" xr:uid="{D651302F-D042-4862-A6DB-0BB033746380}"/>
     <cellStyle name="60% - Accent5 2 2" xfId="59" xr:uid="{FE2BEFF6-0E12-4991-A075-7F4E7295D83E}"/>
     <cellStyle name="60% - Accent5 2 3" xfId="79" xr:uid="{798FC267-B2EC-43A4-8BDA-49DBAA40679F}"/>
     <cellStyle name="60% - Accent5 2 4" xfId="99" xr:uid="{F6376940-A062-4937-A42C-E0D29417FF55}"/>
@@ -1961,6 +2014,7 @@
     <cellStyle name="60% - Accent5 2 9" xfId="199" xr:uid="{18FD24AA-851E-45F7-AB30-AB512A7078C1}"/>
     <cellStyle name="60% - Accent6 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="60% - Accent6 2 10" xfId="220" xr:uid="{905CF6F0-E09C-47DC-AB0E-3F7DF4B67C47}"/>
+    <cellStyle name="60% - Accent6 2 11" xfId="240" xr:uid="{D078B8DD-E234-4FA4-8647-98D715CCC15E}"/>
     <cellStyle name="60% - Accent6 2 2" xfId="60" xr:uid="{BC6F3475-8DD9-4B6B-ABDE-1AA582CBB722}"/>
     <cellStyle name="60% - Accent6 2 3" xfId="80" xr:uid="{9D88C972-D253-4EBD-A14D-03AAFF92FEC0}"/>
     <cellStyle name="60% - Accent6 2 4" xfId="100" xr:uid="{9E2380A9-69E2-41B6-B941-30447272DE59}"/>
@@ -1990,6 +2044,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
     <cellStyle name="Normal 2 10" xfId="221" xr:uid="{48FE9C11-4EBB-44D1-98A8-DF1634DF2D43}"/>
+    <cellStyle name="Normal 2 11" xfId="241" xr:uid="{2538F548-62A5-4C99-8C3D-80A15C9C4C29}"/>
     <cellStyle name="Normal 2 2" xfId="61" xr:uid="{451287C8-17FF-40A8-A01C-88640BF0E8D5}"/>
     <cellStyle name="Normal 2 3" xfId="81" xr:uid="{DE402399-A011-4973-9D21-A6BC70F84FA3}"/>
     <cellStyle name="Normal 2 4" xfId="101" xr:uid="{38C504E4-A2C3-4927-8ADF-536A6B333FFB}"/>
@@ -2000,6 +2055,7 @@
     <cellStyle name="Normal 2 9" xfId="201" xr:uid="{6A91493E-47F1-4E53-A612-8015EBB7D02D}"/>
     <cellStyle name="Note 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="Note 2 10" xfId="222" xr:uid="{32B5DB39-D162-4A30-9DA7-93FED0C190D8}"/>
+    <cellStyle name="Note 2 11" xfId="242" xr:uid="{3FE73286-527A-4D0B-A8F2-F5F6F915F479}"/>
     <cellStyle name="Note 2 2" xfId="62" xr:uid="{C1BF3C78-B53F-41F5-AE7A-0A158154BC25}"/>
     <cellStyle name="Note 2 3" xfId="82" xr:uid="{E721C0C3-0D4F-4BE8-8C4B-21894BCA709E}"/>
     <cellStyle name="Note 2 4" xfId="102" xr:uid="{D718D9A3-3641-46A5-9573-3418425F43A5}"/>
@@ -2443,7 +2499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr transitionEvaluation="1"/>
-  <dimension ref="A1:K855"/>
+  <dimension ref="A1:K876"/>
   <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1" collapsed="1"/>
@@ -17283,6 +17339,258 @@
       </c>
       <c r="D855" s="169"/>
     </row>
+    <row r="856" spans="1:4">
+      <c r="A856" s="171">
+        <v>46149</v>
+      </c>
+      <c r="B856" s="172">
+        <v>6.37</v>
+      </c>
+      <c r="C856" s="172">
+        <v>5.72</v>
+      </c>
+      <c r="D856" s="172"/>
+    </row>
+    <row r="857" spans="1:4">
+      <c r="A857" s="171">
+        <v>46156</v>
+      </c>
+      <c r="B857" s="172">
+        <v>6.36</v>
+      </c>
+      <c r="C857" s="172">
+        <v>5.71</v>
+      </c>
+      <c r="D857" s="172"/>
+    </row>
+    <row r="858" spans="1:4">
+      <c r="A858" s="171">
+        <v>46163</v>
+      </c>
+      <c r="B858" s="172">
+        <v>6.51</v>
+      </c>
+      <c r="C858" s="172">
+        <v>5.85</v>
+      </c>
+      <c r="D858" s="172"/>
+    </row>
+    <row r="859" spans="1:4">
+      <c r="A859" s="171">
+        <v>46170</v>
+      </c>
+      <c r="B859" s="172">
+        <v>6.53</v>
+      </c>
+      <c r="C859" s="172">
+        <v>5.87</v>
+      </c>
+      <c r="D859" s="172"/>
+    </row>
+    <row r="860" spans="1:4">
+      <c r="A860" s="171">
+        <v>46177</v>
+      </c>
+      <c r="B860" s="172">
+        <v>6.48</v>
+      </c>
+      <c r="C860" s="172">
+        <v>5.79</v>
+      </c>
+      <c r="D860" s="172"/>
+    </row>
+    <row r="861" spans="1:4">
+      <c r="A861" s="171">
+        <v>46184</v>
+      </c>
+      <c r="B861" s="172">
+        <v>6.52</v>
+      </c>
+      <c r="C861" s="172">
+        <v>5.84</v>
+      </c>
+      <c r="D861" s="172"/>
+    </row>
+    <row r="862" spans="1:4">
+      <c r="A862" s="171">
+        <v>46191</v>
+      </c>
+      <c r="B862" s="172">
+        <v>6.47</v>
+      </c>
+      <c r="C862" s="172">
+        <v>5.81</v>
+      </c>
+      <c r="D862" s="172"/>
+    </row>
+    <row r="863" spans="1:4">
+      <c r="A863" s="171">
+        <v>46198</v>
+      </c>
+      <c r="B863" s="172">
+        <v>6.49</v>
+      </c>
+      <c r="C863" s="172">
+        <v>5.84</v>
+      </c>
+      <c r="D863" s="172"/>
+    </row>
+    <row r="864" spans="1:4">
+      <c r="A864" s="171">
+        <v>46205</v>
+      </c>
+      <c r="B864" s="172">
+        <v>6.43</v>
+      </c>
+      <c r="C864" s="172">
+        <v>5.79</v>
+      </c>
+      <c r="D864" s="172"/>
+    </row>
+    <row r="865" spans="1:4">
+      <c r="A865" s="171">
+        <v>46212</v>
+      </c>
+      <c r="B865" s="172">
+        <v>6.49</v>
+      </c>
+      <c r="C865" s="172">
+        <v>5.82</v>
+      </c>
+      <c r="D865" s="172"/>
+    </row>
+    <row r="866" spans="1:4">
+      <c r="A866" s="171">
+        <v>46219</v>
+      </c>
+      <c r="B866" s="172">
+        <v>6.55</v>
+      </c>
+      <c r="C866" s="172">
+        <v>5.93</v>
+      </c>
+      <c r="D866" s="172"/>
+    </row>
+    <row r="867" spans="1:4">
+      <c r="A867" s="171">
+        <v>46226</v>
+      </c>
+      <c r="B867" s="172">
+        <v>6.58</v>
+      </c>
+      <c r="C867" s="172">
+        <v>5.96</v>
+      </c>
+      <c r="D867" s="172"/>
+    </row>
+    <row r="868" spans="1:4">
+      <c r="A868" s="171">
+        <v>46233</v>
+      </c>
+      <c r="B868" s="172">
+        <v>6.66</v>
+      </c>
+      <c r="C868" s="172">
+        <v>6.04</v>
+      </c>
+      <c r="D868" s="172"/>
+    </row>
+    <row r="869" spans="1:4">
+      <c r="A869" s="171">
+        <v>46240</v>
+      </c>
+      <c r="B869" s="172">
+        <v>6.69</v>
+      </c>
+      <c r="C869" s="172">
+        <v>6.01</v>
+      </c>
+      <c r="D869" s="172"/>
+    </row>
+    <row r="870" spans="1:4">
+      <c r="A870" s="171">
+        <v>46247</v>
+      </c>
+      <c r="B870" s="172">
+        <v>6.67</v>
+      </c>
+      <c r="C870" s="172">
+        <v>5.96</v>
+      </c>
+      <c r="D870" s="172"/>
+    </row>
+    <row r="871" spans="1:4">
+      <c r="A871" s="171">
+        <v>46254</v>
+      </c>
+      <c r="B871" s="172">
+        <v>6.65</v>
+      </c>
+      <c r="C871" s="172">
+        <v>5.95</v>
+      </c>
+      <c r="D871" s="172"/>
+    </row>
+    <row r="872" spans="1:4">
+      <c r="A872" s="171">
+        <v>46261</v>
+      </c>
+      <c r="B872" s="172">
+        <v>6.66</v>
+      </c>
+      <c r="C872" s="172">
+        <v>5.98</v>
+      </c>
+      <c r="D872" s="172"/>
+    </row>
+    <row r="873" spans="1:4">
+      <c r="A873" s="171">
+        <v>46268</v>
+      </c>
+      <c r="B873" s="172">
+        <v>6.71</v>
+      </c>
+      <c r="C873" s="172">
+        <v>6.04</v>
+      </c>
+      <c r="D873" s="172"/>
+    </row>
+    <row r="874" spans="1:4">
+      <c r="A874" s="171">
+        <v>46275</v>
+      </c>
+      <c r="B874" s="172">
+        <v>6.76</v>
+      </c>
+      <c r="C874" s="172">
+        <v>6.09</v>
+      </c>
+      <c r="D874" s="172"/>
+    </row>
+    <row r="875" spans="1:4">
+      <c r="A875" s="171">
+        <v>46282</v>
+      </c>
+      <c r="B875" s="172">
+        <v>6.95</v>
+      </c>
+      <c r="C875" s="172">
+        <v>6.26</v>
+      </c>
+      <c r="D875" s="172"/>
+    </row>
+    <row r="876" spans="1:4">
+      <c r="A876" s="171">
+        <v>46289</v>
+      </c>
+      <c r="B876" s="172">
+        <v>7.03</v>
+      </c>
+      <c r="C876" s="172">
+        <v>6.42</v>
+      </c>
+      <c r="D876" s="172"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLinesSet="0"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.25" footer="0.25"/>
